--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487665_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487665_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5297</v>
+        <v>2.8648</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.4253</v>
+        <v>-0.5216</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9549</v>
+        <v>3.3864</v>
       </c>
       <c r="G2" t="n">
-        <v>4.932</v>
+        <v>6.7908</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5013</v>
+        <v>4.528</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4308</v>
+        <v>2.2628</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5754</v>
+        <v>4.2397</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3347</v>
+        <v>3.5674</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2407</v>
+        <v>0.6724</v>
       </c>
       <c r="M2" t="n">
-        <v>2.3566</v>
+        <v>2.5511</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1666</v>
+        <v>0.9606</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1901</v>
+        <v>1.5904</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.3582</v>
+        <v>-2.7164</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.8806</v>
+        <v>-5.0448</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5224</v>
+        <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1797</v>
+        <v>-0.2678</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.12</v>
+        <v>-0.2807</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2997</v>
+        <v>0.0129</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2239</v>
+        <v>-0.9418</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5561</v>
+        <v>2.6452</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4215</v>
+        <v>-1.4648</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9776</v>
+        <v>4.11</v>
       </c>
       <c r="G3" t="n">
-        <v>6.7908</v>
+        <v>4.932</v>
       </c>
       <c r="H3" t="n">
-        <v>4.528</v>
+        <v>2.5013</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2628</v>
+        <v>2.4308</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2397</v>
+        <v>2.5754</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5674</v>
+        <v>1.3347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6724</v>
+        <v>1.2407</v>
       </c>
       <c r="M3" t="n">
-        <v>2.5511</v>
+        <v>2.3566</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9606</v>
+        <v>1.1666</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5904</v>
+        <v>1.1901</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.7164</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.0448</v>
+        <v>-3.8806</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3284</v>
+        <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5765</v>
+        <v>0.2953</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1806</v>
+        <v>-0.1596</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3959</v>
+        <v>0.4549</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9418</v>
+        <v>-1.2239</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9842</v>
+        <v>2.4659</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2676</v>
+        <v>0.3677</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7166</v>
+        <v>2.0981</v>
       </c>
       <c r="G4" t="n">
         <v>1.2177</v>
@@ -766,13 +766,13 @@
         <v>0.7761</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1767</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.424</v>
+        <v>-0.3239</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7528</v>
+        <v>-0.3712</v>
       </c>
       <c r="V4" t="n">
         <v>3.1075</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4914</v>
+        <v>1.5821</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4838</v>
+        <v>-1.5839</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9752</v>
+        <v>3.166</v>
       </c>
       <c r="G5" t="n">
         <v>0.8925</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0309</v>
+        <v>0.0597</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0011</v>
+        <v>-0.099</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.032</v>
+        <v>0.1587</v>
       </c>
       <c r="V5" t="n">
         <v>0.0478</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3437</v>
+        <v>1.2591</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0827</v>
+        <v>-1.9221</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4264</v>
+        <v>3.1811</v>
       </c>
       <c r="G6" t="n">
         <v>2.7654</v>
@@ -922,13 +922,13 @@
         <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9172</v>
+        <v>-1.0018</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6662</v>
+        <v>-0.5056</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.251</v>
+        <v>-0.4963</v>
       </c>
       <c r="V6" t="n">
         <v>0.6597</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0379</v>
+        <v>0.9388</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1513</v>
+        <v>-1.6508</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1891</v>
+        <v>2.5895</v>
       </c>
       <c r="G7" t="n">
         <v>0.5586</v>
@@ -1000,13 +1000,13 @@
         <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5077</v>
+        <v>0.4085</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9085</v>
+        <v>-0.408</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4161</v>
+        <v>0.8165</v>
       </c>
       <c r="V7" t="n">
         <v>0.9418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0413</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0876</v>
+        <v>-3.2845</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0463</v>
+        <v>3.2131</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3047</v>
+        <v>0.7143</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.0533</v>
+        <v>1.2243</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7485000000000001</v>
+        <v>-0.51</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9634</v>
+        <v>0.0489</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.5952</v>
+        <v>1.3429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6318</v>
+        <v>-1.2941</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3413</v>
+        <v>0.6654</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4581</v>
+        <v>-0.1187</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1168</v>
+        <v>0.7841</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1642</v>
+        <v>-2.9105</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9403</v>
+        <v>2.3284</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.2036</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3017</v>
+        <v>-0.4229</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3288</v>
+        <v>0.2193</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3227</v>
+        <v>-0.172</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.345</v>
+        <v>-0.3273</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0223</v>
+        <v>0.1553</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7143</v>
+        <v>-2.3047</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2243</v>
+        <v>-3.0533</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.51</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0489</v>
+        <v>-1.9634</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3429</v>
+        <v>-2.5952</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2941</v>
+        <v>0.6318</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6654</v>
+        <v>-0.3413</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1187</v>
+        <v>-0.4581</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7841</v>
+        <v>0.1168</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4549</v>
+        <v>-0.7613</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4834</v>
+        <v>-0.5415</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0285</v>
+        <v>-0.2198</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.3418</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3606</v>
+        <v>-1.7455</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9387</v>
+        <v>-2.678</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.9325</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2381</v>
@@ -1234,13 +1234,13 @@
         <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9464</v>
+        <v>-1.3313</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8479</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0985</v>
+        <v>-0.7441</v>
       </c>
       <c r="V10" t="n">
         <v>0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6682</v>
+        <v>-2.914</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4104</v>
+        <v>-2.7107</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2579</v>
+        <v>-0.2034</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6492</v>
@@ -1312,13 +1312,13 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.631</v>
+        <v>-0.8768</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0617</v>
+        <v>-0.2386</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6927</v>
+        <v>-0.6381</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.550199999999998</v>
+        <v>6.853</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.0787</v>
+        <v>-15.776</v>
       </c>
       <c r="F12" t="n">
         <v>22.6286</v>
@@ -1390,13 +1390,13 @@
         <v>16.4927</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.6767</v>
+        <v>-4.3742</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.8695</v>
+        <v>-3.567</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8074000000000001</v>
+        <v>-0.8071999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>5.3687</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7302</v>
+        <v>5.4125</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7796</v>
+        <v>2.3802</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9505</v>
+        <v>3.0323</v>
       </c>
       <c r="G13" t="n">
         <v>1.5681</v>
@@ -1468,13 +1468,13 @@
         <v>3.4926</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4783</v>
+        <v>0.2041</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8345</v>
+        <v>-0.2339</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3562</v>
+        <v>0.438</v>
       </c>
       <c r="V13" t="n">
         <v>1.506</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7602</v>
+        <v>1.8936</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9424</v>
+        <v>0.8166</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8177</v>
+        <v>1.077</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.8732</v>
+        <v>-0.2165</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.127</v>
+        <v>0.1895</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7462</v>
+        <v>-0.406</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.694</v>
+        <v>-0.0659</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3594</v>
+        <v>-0.0659</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3347</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1792</v>
+        <v>-0.1506</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2323</v>
+        <v>0.2554</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4115</v>
+        <v>-0.406</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6334</v>
+        <v>0.722</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1007</v>
+        <v>0.4646</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.2574</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8358</v>
+        <v>0.6119</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1179</v>
+        <v>0.6119</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6216</v>
+        <v>1.4849</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5173</v>
+        <v>-1.7576</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1042</v>
+        <v>3.2425</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2165</v>
+        <v>2.7496</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1895</v>
+        <v>3.6316</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.406</v>
+        <v>-0.882</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0659</v>
+        <v>1.983</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0659</v>
+        <v>2.587</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.6039</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1506</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2554</v>
+        <v>1.0447</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.406</v>
+        <v>-0.2781</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7761</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.194</v>
+        <v>-2.3284</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>1.45</v>
+        <v>0.4427</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1653</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2847</v>
+        <v>0.5356</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6119</v>
+        <v>-1.3194</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6119</v>
+        <v>-1.3194</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5602</v>
+        <v>1.3588</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0588</v>
+        <v>-0.459</v>
       </c>
       <c r="F16" t="n">
-        <v>1.619</v>
+        <v>1.8177</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5024</v>
+        <v>-2.8732</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1532</v>
+        <v>-1.127</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-1.7462</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3441</v>
+        <v>-2.694</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3213</v>
+        <v>-1.3594</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0228</v>
+        <v>-1.3347</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8466</v>
+        <v>-0.1792</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1681</v>
+        <v>0.2323</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6785</v>
+        <v>-0.4115</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="R16" t="n">
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2626</v>
+        <v>1.232</v>
       </c>
       <c r="T16" t="n">
-        <v>1.421</v>
+        <v>0.6993</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8416</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7821</v>
+        <v>1.8358</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6597</v>
+        <v>2.1179</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1224</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9026</v>
+        <v>1.2668</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2581</v>
+        <v>-1.2523</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1607</v>
+        <v>2.5191</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7496</v>
+        <v>0.0502</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6316</v>
+        <v>1.838</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.882</v>
+        <v>-1.7879</v>
       </c>
       <c r="J17" t="n">
-        <v>1.983</v>
+        <v>1.0529</v>
       </c>
       <c r="K17" t="n">
-        <v>2.587</v>
+        <v>1.7507</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6039</v>
+        <v>-0.6979</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7665999999999999</v>
+        <v>-1.0027</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0447</v>
+        <v>0.0873</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2781</v>
+        <v>-1.09</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.3284</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>2.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1395</v>
+        <v>0.6345</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5933</v>
+        <v>0.0232</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4538</v>
+        <v>0.6113</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3194</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.3194</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2202</v>
+        <v>0.4051</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3534</v>
+        <v>-0.8596</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5736</v>
+        <v>1.2647</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0502</v>
+        <v>-0.5024</v>
       </c>
       <c r="H18" t="n">
-        <v>1.838</v>
+        <v>0.1532</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7879</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0529</v>
+        <v>0.3441</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7507</v>
+        <v>0.3213</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6979</v>
+        <v>0.0228</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0027</v>
+        <v>-0.8466</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0873</v>
+        <v>-0.1681</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.09</v>
+        <v>-0.6785</v>
       </c>
       <c r="P18" t="n">
         <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3284</v>
+        <v>-1.1642</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9105</v>
+        <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4121</v>
+        <v>1.1075</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0779</v>
+        <v>0.6202</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.4873</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.7821</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6642</v>
+        <v>-3.0557</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2202</v>
+        <v>-3.7206</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.6649</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6421</v>
@@ -1936,13 +1936,13 @@
         <v>3.1045</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8017</v>
+        <v>0.4102</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4273</v>
+        <v>-0.0732</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3744</v>
+        <v>0.4834</v>
       </c>
       <c r="V19" t="n">
         <v>-2.5701</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4487</v>
+        <v>-3.8208</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.149</v>
+        <v>-5.5484</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7003</v>
+        <v>1.7276</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4444</v>
@@ -2014,13 +2014,13 @@
         <v>1.7463</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.166</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8838</v>
+        <v>-0.2832</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09</v>
+        <v>0.1172</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0164</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6251</v>
+        <v>-5.6794</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0906</v>
+        <v>-7.1375</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5345</v>
+        <v>1.4581</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3305</v>
+        <v>-5.0381</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.058</v>
+        <v>-2.1602</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2725</v>
+        <v>-2.8779</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5457</v>
+        <v>-4.6908</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.8784</v>
+        <v>-1.5571</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6673</v>
+        <v>-3.1337</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2152</v>
+        <v>-0.3473</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1796</v>
+        <v>-0.6031</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3948</v>
+        <v>0.2558</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3284</v>
+        <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5523</v>
+        <v>3.1045</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3338</v>
+        <v>-0.0533</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2165</v>
+        <v>-0.1004</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5503</v>
+        <v>0.0471</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.8522</v>
+        <v>-0.7821</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.8522</v>
+        <v>-1.3463</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6071</v>
+        <v>-5.8159</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.7381</v>
+        <v>-5.0906</v>
       </c>
       <c r="F22" t="n">
-        <v>1.131</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.0381</v>
+        <v>-2.3305</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1602</v>
+        <v>-2.058</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8779</v>
+        <v>-0.2725</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.6908</v>
+        <v>-2.5457</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5571</v>
+        <v>-1.8784</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.1337</v>
+        <v>-0.6673</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3473</v>
+        <v>0.2152</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6031</v>
+        <v>-0.1796</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2558</v>
+        <v>0.3948</v>
       </c>
       <c r="P22" t="n">
-        <v>0.194</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9105</v>
+        <v>-2.3284</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1045</v>
+        <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.981</v>
+        <v>0.143</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.701</v>
+        <v>-0.2165</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2799</v>
+        <v>0.3595</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7821</v>
+        <v>-2.8522</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3463</v>
+        <v>-2.8522</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5501</v>
+        <v>-6.550100000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.6289</v>
+        <v>-22.6288</v>
       </c>
       <c r="F23" t="n">
-        <v>16.0784</v>
+        <v>16.0786</v>
       </c>
       <c r="G23" t="n">
         <v>-11.6793</v>
@@ -2218,7 +2218,7 @@
         <v>-4.3665</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.312900000000001</v>
+        <v>-7.312900000000002</v>
       </c>
       <c r="J23" t="n">
         <v>-9.1044</v>
@@ -2239,7 +2239,7 @@
         <v>-1.4461</v>
       </c>
       <c r="P23" t="n">
-        <v>5.820999999999999</v>
+        <v>5.821</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.4927</v>
@@ -2248,13 +2248,13 @@
         <v>22.3138</v>
       </c>
       <c r="S23" t="n">
-        <v>4.6767</v>
+        <v>4.676699999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8072999999999998</v>
+        <v>0.8073</v>
       </c>
       <c r="U23" t="n">
-        <v>3.869699999999999</v>
+        <v>3.8696</v>
       </c>
       <c r="V23" t="n">
         <v>-5.368599999999999</v>
@@ -2263,7 +2263,7 @@
         <v>2.1612</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.529800000000001</v>
+        <v>-7.5298</v>
       </c>
     </row>
   </sheetData>
